--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_UEMC BALONCESTO VALLADOLID.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_UEMC BALONCESTO VALLADOLID.xlsx
@@ -1321,7 +1321,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>E. GUTIERREZ O CALLAGHAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
